--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/user-service/createMemberWithTempPassword-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/user-service/createMemberWithTempPassword-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="80">
-  <si>
-    <t>Statement: UserService.createMemberWithTempPassword(data) – Generates a cryptographically random 16-character temporary password (guaranteed uppercase, digit, special char via crypto.getRandomValues). Calls createMember() with temp password. Returns member + plaintext temp password.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="42">
+  <si>
+    <t>Statement: UserService.createMemberWithTempPassword(data)</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: CreateMemberWithTempPasswordInput { email, fullName, phone, dateOfBirth, membershipStart } (no password field)</t>
+    <t>Input: CreateMemberWithTempPasswordInput</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>userRepository is accessible  |  crypto.getRandomValues is available</t>
+    <t>userRepository accessible</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: Promise&lt;MemberWithUserAndTempPassword&gt;  OR  throws ConflictError</t>
+    <t>Output: Promise&lt;MemberWithUserAndTempPassword&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>On success: MemberWithUser + tempPassword (plaintext 16-char) returned. Password never stored in plaintext.</t>
+    <t>Member created with temp pwd.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,39 +64,6 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>temp password length</t>
-  </si>
-  <si>
-    <t>generated password is exactly 16 characters</t>
-  </si>
-  <si>
-    <t>temp password uppercase</t>
-  </si>
-  <si>
-    <t>contains at least one uppercase letter</t>
-  </si>
-  <si>
-    <t>temp password digit</t>
-  </si>
-  <si>
-    <t>contains at least one digit</t>
-  </si>
-  <si>
-    <t>temp password special</t>
-  </si>
-  <si>
-    <t>contains at least one special character</t>
-  </si>
-  <si>
-    <t>email uniqueness</t>
-  </si>
-  <si>
-    <t>email not taken – delegate creates member</t>
-  </si>
-  <si>
-    <t>email taken – ConflictError propagated</t>
-  </si>
-  <si>
     <t>No TC</t>
   </si>
   <si>
@@ -112,109 +79,28 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Valid input, mock repo returns MemberWithUser</t>
-  </si>
-  <si>
-    <t>result.tempPassword.length === 16</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Same as TC-1</t>
-  </si>
-  <si>
-    <t>/[A-Z]/.test(result.tempPassword) === true</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>/[0-9]/.test(result.tempPassword) === true</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>/[^A-Za-z0-9]/.test(result.tempPassword) === true</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Duplicate email, repo throws ConflictError</t>
-  </si>
-  <si>
-    <t>Throws ConflictError</t>
-  </si>
-  <si>
     <t>Number BVA</t>
   </si>
   <si>
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>password length</t>
-  </si>
-  <si>
-    <t>Exact boundary: generated password must be exactly 16 chars (not 15, not 17)</t>
-  </si>
-  <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1</t>
-  </si>
-  <si>
-    <t>Call createMemberWithTempPassword with valid input</t>
-  </si>
-  <si>
-    <t>result.tempPassword.length === 16 (exactly at boundary)</t>
-  </si>
-  <si>
     <t>TC from EC</t>
   </si>
   <si>
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
-    <t>Valid input, mock repo succeeds</t>
-  </si>
-  <si>
-    <t>tempPassword is exactly 16 chars</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
-    <t>Same valid input</t>
-  </si>
-  <si>
-    <t>tempPassword has uppercase letter</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
-    <t>tempPassword has digit</t>
-  </si>
-  <si>
-    <t>EP-4</t>
-  </si>
-  <si>
-    <t>tempPassword has special char</t>
-  </si>
-  <si>
-    <t>EP-5</t>
-  </si>
-  <si>
-    <t>Duplicate email</t>
+    <t>Create with temp pwd</t>
+  </si>
+  <si>
+    <t>Success/Error</t>
+  </si>
+  <si>
+    <t>Passed</t>
   </si>
   <si>
     <t>Testing</t>
@@ -772,7 +658,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -794,76 +680,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -872,7 +688,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -884,104 +700,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -992,7 +723,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1002,24 +733,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1030,7 +750,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1042,36 +762,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1082,7 +785,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1095,22 +798,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1118,19 +821,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1138,19 +841,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1158,19 +861,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1178,39 +881,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1238,16 +921,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1255,45 +938,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1302,19 +985,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/user-service/createMemberWithTempPassword-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/user-service/createMemberWithTempPassword-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="42">
-  <si>
-    <t>Statement: UserService.createMemberWithTempPassword(data)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="57">
+  <si>
+    <t>Statement: UserService.createMemberWithTempPassword(data) – Creates a new member account and generates a temporary password. Returns MemberWithUserAndTempPassword on success. Throws ConflictError if the email is already registered.</t>
   </si>
   <si>
     <t/>
@@ -31,13 +31,13 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: CreateMemberWithTempPasswordInput</t>
+    <t>Input: CreateMemberWithTempPasswordInput { email, fullName, phone, dateOfBirth, membershipStart }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>userRepository accessible</t>
+    <t>Input data is provided. User with the given email may or may not already exist in the system.</t>
   </si>
   <si>
     <t>Results</t>
@@ -49,7 +49,7 @@
     <t>postcondition</t>
   </si>
   <si>
-    <t>Member created with temp pwd.</t>
+    <t>On success: MemberWithUserAndTempPassword returned with id, user.email matching input, and a 16-character generated temporary password. On failure: ConflictError thrown.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,6 +64,15 @@
     <t>Invalid EC</t>
   </si>
   <si>
+    <t>Email registration</t>
+  </si>
+  <si>
+    <t>New (unregistered) email → MemberWithUserAndTempPassword returned</t>
+  </si>
+  <si>
+    <t>Already registered email → ConflictError</t>
+  </si>
+  <si>
     <t>No TC</t>
   </si>
   <si>
@@ -79,30 +88,66 @@
     <t>Actual Result</t>
   </si>
   <si>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>john@example.com (new email)</t>
+  </si>
+  <si>
+    <t>MemberWithUserAndTempPassword returned, id set, user.email matches input, tempPassword has length 16</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>taken@example.com (taken email)</t>
+  </si>
+  <si>
+    <t>throws ConflictError("Email taken")</t>
+  </si>
+  <si>
     <t>Number BVA</t>
   </si>
   <si>
     <t>BVA Test Case</t>
   </si>
   <si>
+    <t>Temporary password length</t>
+  </si>
+  <si>
+    <t>Exactly 16 characters</t>
+  </si>
+  <si>
+    <t>Temporary password strength</t>
+  </si>
+  <si>
+    <t>Contains at least one uppercase letter, one digit, and one special character</t>
+  </si>
+  <si>
     <t>BVA</t>
   </si>
   <si>
+    <t>BVA-1</t>
+  </si>
+  <si>
+    <t>tempPassword is exactly 16 characters long</t>
+  </si>
+  <si>
+    <t>BVA-2</t>
+  </si>
+  <si>
+    <t>tempPassword contains uppercase letter, digit, and special character</t>
+  </si>
+  <si>
     <t>TC from EC</t>
   </si>
   <si>
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Create with temp pwd</t>
-  </si>
-  <si>
-    <t>Success/Error</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -133,7 +178,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>MEM-02</t>
+    <t>SERV-03</t>
   </si>
   <si>
     <t>n/a</t>
@@ -658,7 +703,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -680,6 +725,34 @@
         <v>14</v>
       </c>
     </row>
+    <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -688,7 +761,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -700,19 +773,53 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -723,7 +830,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -733,13 +840,35 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>21</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -750,7 +879,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -762,19 +891,53 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>19</v>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -798,22 +961,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -821,19 +984,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -841,19 +1004,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -861,19 +1024,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -881,19 +1044,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -921,16 +1084,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -938,39 +1101,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B3" s="1">
         <v>4</v>
@@ -985,19 +1148,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/user-service/createMemberWithTempPassword-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/user-service/createMemberWithTempPassword-bbt-form.xlsx
@@ -178,7 +178,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SERV-03</t>
+    <t>SERV-04</t>
   </si>
   <si>
     <t>n/a</t>
